--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488163_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488163_PROCESSED_CHRONO.xlsx
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1282</v>
+        <v>0.5205</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4247</v>
+        <v>3.7185</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.2965</v>
+        <v>-3.198</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5183</v>
@@ -766,13 +766,13 @@
         <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4838</v>
+        <v>-1.0915</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0396</v>
+        <v>-0.7458</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4442</v>
+        <v>-0.3457</v>
       </c>
       <c r="V4" t="n">
         <v>1.5744</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>C. CORRALES GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.727</v>
+        <v>-1.8988</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2819</v>
+        <v>-0.1974</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.0089</v>
+        <v>-1.7014</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9309</v>
+        <v>-0.5762</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2379</v>
+        <v>-0.7068</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1688</v>
+        <v>0.1306</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7855</v>
+        <v>0.0215</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0959</v>
+        <v>0.0215</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3104</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.7164</v>
+        <v>-0.5977</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.858</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8584</v>
+        <v>0.1306</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.286</v>
+        <v>-0.3084</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1504</v>
+        <v>-0.2189</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1356</v>
+        <v>-0.0895</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2512</v>
+        <v>-1.3847</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8245</v>
+        <v>-1.3847</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. CORRALES GARCIA</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9234</v>
+        <v>-2.169</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1974</v>
+        <v>3.086</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.726</v>
+        <v>-5.2551</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5762</v>
+        <v>-1.9309</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7068</v>
+        <v>0.2379</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1306</v>
+        <v>-2.1688</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0215</v>
+        <v>2.7855</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0215</v>
+        <v>3.0959</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.3104</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5977</v>
+        <v>-4.7164</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-2.858</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1306</v>
+        <v>-1.8584</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.333</v>
+        <v>-0.7281</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2189</v>
+        <v>-0.3463</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1142</v>
+        <v>-0.3818</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3847</v>
+        <v>-0.2512</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3847</v>
+        <v>-1.8245</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1557</v>
+        <v>-2.3526</v>
       </c>
       <c r="E7" t="n">
         <v>-0.4414</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7143</v>
+        <v>-1.9113</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4074</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0664</v>
+        <v>-0.1306</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2736</v>
       </c>
       <c r="U7" t="n">
-        <v>0.34</v>
+        <v>0.143</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2589</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1929</v>
+        <v>-2.6333</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7795</v>
+        <v>-2.2692</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4134</v>
+        <v>-0.3641</v>
       </c>
       <c r="G8" t="n">
         <v>-4.4792</v>
@@ -1078,13 +1078,13 @@
         <v>2.594</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2445</v>
+        <v>-0.6849</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1779</v>
+        <v>-0.3118</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4223</v>
+        <v>-0.3731</v>
       </c>
       <c r="V8" t="n">
         <v>-0.06320000000000001</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.242</v>
+        <v>-2.801</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1425</v>
+        <v>-1.7508</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0995</v>
+        <v>-1.0502</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0219</v>
@@ -1156,13 +1156,13 @@
         <v>1.1117</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.723</v>
+        <v>-1.2821</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0396</v>
+        <v>-0.6479</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6835</v>
+        <v>-0.6342</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7559</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1297</v>
+        <v>-4.1537</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9052</v>
+        <v>0.8073</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.0349</v>
+        <v>-4.961</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5955</v>
@@ -1234,13 +1234,13 @@
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8138</v>
+        <v>-0.8378</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2226</v>
+        <v>-0.3205</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.5173</v>
       </c>
       <c r="V10" t="n">
         <v>-2.8321</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8633</v>
+        <v>-4.7654</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5679</v>
+        <v>-2.4699</v>
       </c>
       <c r="F11" t="n">
         <v>-2.2955</v>
@@ -1312,10 +1312,10 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0634</v>
+        <v>0.1614</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1269</v>
+        <v>0.2248</v>
       </c>
       <c r="U11" t="n">
         <v>-0.0634</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. LLAMAS JIMENEZ</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.92</v>
+        <v>-5.8408</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2904</v>
+        <v>-1.9448</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6296</v>
+        <v>-3.896</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.4499</v>
+        <v>-4.7351</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.8461</v>
+        <v>-3.3066</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6038</v>
+        <v>-1.4285</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9101</v>
+        <v>-1.6224</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.4658</v>
+        <v>-0.524</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4443</v>
+        <v>-1.0984</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.5398</v>
+        <v>-3.1127</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.3803</v>
+        <v>-2.7825</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1596</v>
+        <v>-0.3301</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2234</v>
+        <v>1.297</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2234</v>
+        <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9458</v>
+        <v>-0.2627</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6392</v>
+        <v>-0.3224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3067</v>
+        <v>0.0597</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2523</v>
+        <v>-2.14</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0065</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>A. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0126</v>
+        <v>-5.8959</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0427</v>
+        <v>-2.1925</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9699</v>
+        <v>-3.7034</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.7351</v>
+        <v>-7.4499</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.3066</v>
+        <v>-5.8461</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4285</v>
+        <v>-1.6038</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6224</v>
+        <v>-2.9101</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.524</v>
+        <v>-2.4658</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0984</v>
+        <v>-0.4443</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1127</v>
+        <v>-4.5398</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.7825</v>
+        <v>-3.3803</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3301</v>
+        <v>-1.1596</v>
       </c>
       <c r="P13" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4345</v>
+        <v>-0.9218</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4203</v>
+        <v>-0.5412</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0142</v>
+        <v>-0.3805</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.14</v>
+        <v>0.2523</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.14</v>
+        <v>-1.0065</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.5151</v>
+        <v>-6.5633</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.348</v>
+        <v>-1.5438</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.1672</v>
+        <v>-5.0195</v>
       </c>
       <c r="G14" t="n">
         <v>-3.7962</v>
@@ -1546,13 +1546,13 @@
         <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4634</v>
+        <v>-1.5115</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.715</v>
+        <v>-0.9109</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7484</v>
+        <v>-0.6006</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0703</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-34.7991</v>
+        <v>-34.7989</v>
       </c>
       <c r="E15" t="n">
         <v>-1.4436</v>
       </c>
       <c r="F15" t="n">
-        <v>-33.3557</v>
+        <v>-33.3555</v>
       </c>
       <c r="G15" t="n">
         <v>-25.1723</v>
@@ -1600,7 +1600,7 @@
         <v>3.7754</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.250200000000001</v>
+        <v>-3.2502</v>
       </c>
       <c r="L15" t="n">
         <v>7.025499999999999</v>
@@ -1624,13 +1624,13 @@
         <v>14.8229</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.598</v>
+        <v>-7.597999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.4144</v>
+        <v>-4.4145</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.1837</v>
+        <v>-3.1834</v>
       </c>
       <c r="V15" t="n">
         <v>-9.440200000000001</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ROPERO BENIEZ</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6778</v>
+        <v>5.2602</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9706</v>
+        <v>6.0556</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7072000000000001</v>
+        <v>-0.7954</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9366</v>
+        <v>2.5876</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0717</v>
+        <v>3.2741</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1351</v>
+        <v>-0.6865</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3859</v>
+        <v>3.8833</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9237</v>
+        <v>3.1261</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4622</v>
+        <v>0.7572</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4493</v>
+        <v>-1.2957</v>
       </c>
       <c r="N16" t="n">
         <v>0.148</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5973</v>
+        <v>-1.4437</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1117</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>-2.0382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0207</v>
+        <v>1.3222</v>
       </c>
       <c r="T16" t="n">
-        <v>0.291</v>
+        <v>0.7489</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7297</v>
+        <v>0.5733</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8321</v>
+        <v>2.8327</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1466</v>
+        <v>3.4616</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>J. ROPERO BENIEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5774</v>
+        <v>5.1853</v>
       </c>
       <c r="E17" t="n">
-        <v>6.5452</v>
+        <v>4.9706</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9678</v>
+        <v>0.2148</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5876</v>
+        <v>1.9366</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2741</v>
+        <v>2.0717</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6865</v>
+        <v>-0.1351</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8833</v>
+        <v>3.3859</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1261</v>
+        <v>1.9237</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7572</v>
+        <v>1.4622</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2957</v>
+        <v>-1.4493</v>
       </c>
       <c r="N17" t="n">
         <v>0.148</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4437</v>
+        <v>-1.5973</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4823</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0382</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6395</v>
+        <v>1.5283</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2386</v>
+        <v>0.291</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4009</v>
+        <v>1.2373</v>
       </c>
       <c r="V17" t="n">
-        <v>2.8327</v>
+        <v>2.8321</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4616</v>
+        <v>3.1466</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.0413</v>
+        <v>4.4349</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4628</v>
+        <v>2.169</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5786</v>
+        <v>2.266</v>
       </c>
       <c r="G18" t="n">
         <v>1.8048</v>
@@ -1858,13 +1858,13 @@
         <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0513</v>
+        <v>0.4449</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2151</v>
+        <v>-0.0786</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8361</v>
+        <v>0.5235</v>
       </c>
       <c r="V18" t="n">
         <v>1.2589</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4221</v>
+        <v>3.9204</v>
       </c>
       <c r="E19" t="n">
-        <v>4.0137</v>
+        <v>2.7465</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5916</v>
+        <v>1.1739</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2565</v>
+        <v>1.7313</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5239</v>
+        <v>-0.3882</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7325</v>
+        <v>2.1196</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4827</v>
+        <v>2.5429</v>
       </c>
       <c r="K19" t="n">
-        <v>1.46</v>
+        <v>-0.0604</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0227</v>
+        <v>2.6033</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2263</v>
+        <v>-0.8115</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0639</v>
+        <v>-0.3278</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2901</v>
+        <v>-0.4837</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7951</v>
+        <v>0.8179</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7163</v>
+        <v>0.2036</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0788</v>
+        <v>0.6143</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.3997</v>
+        <v>3.8988</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7016</v>
+        <v>2.987</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6981</v>
+        <v>0.9117</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8421999999999999</v>
+        <v>4.5668</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5349</v>
+        <v>2.5331</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6927</v>
+        <v>2.0337</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0814</v>
+        <v>3.1214</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5193</v>
+        <v>1.8251</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6007</v>
+        <v>1.2963</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9236</v>
+        <v>1.4455</v>
       </c>
       <c r="N20" t="n">
-        <v>1.0156</v>
+        <v>0.708</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.092</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1117</v>
+        <v>-2.7793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2191</v>
+        <v>-0.074</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2524</v>
+        <v>-0.1871</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0333</v>
+        <v>0.1131</v>
       </c>
       <c r="V20" t="n">
-        <v>3.1471</v>
+        <v>1.2589</v>
       </c>
       <c r="W20" t="n">
-        <v>3.1471</v>
+        <v>2.8321</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2769</v>
+        <v>3.8973</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7912</v>
+        <v>2.0933</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4857</v>
+        <v>1.804</v>
       </c>
       <c r="G21" t="n">
-        <v>4.5668</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5331</v>
+        <v>1.5349</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0337</v>
+        <v>-0.6927</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1214</v>
+        <v>-0.0814</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8251</v>
+        <v>0.5193</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2963</v>
+        <v>-0.6007</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4455</v>
+        <v>0.9236</v>
       </c>
       <c r="N21" t="n">
-        <v>0.708</v>
+        <v>1.0156</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7374000000000001</v>
+        <v>-0.092</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8529</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7793</v>
+        <v>-1.1117</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6959</v>
+        <v>0.2785</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.383</v>
+        <v>0.1393</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3129</v>
+        <v>0.1393</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>3.1471</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8321</v>
+        <v>3.1471</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2338</v>
+        <v>3.5217</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2569</v>
+        <v>3.8179</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9769</v>
+        <v>-0.2961</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7313</v>
+        <v>2.2565</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3882</v>
+        <v>1.5239</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1196</v>
+        <v>0.7325</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5429</v>
+        <v>3.4827</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0604</v>
+        <v>1.46</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6033</v>
+        <v>2.0227</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8115</v>
+        <v>-1.2263</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3278</v>
+        <v>0.0639</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4837</v>
+        <v>-1.2901</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1313</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.286</v>
+        <v>0.5204</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4173</v>
+        <v>0.3743</v>
       </c>
       <c r="V22" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.0006</v>
+        <v>3.3474</v>
       </c>
       <c r="E23" t="n">
-        <v>3.9434</v>
+        <v>2.4559</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9428</v>
+        <v>0.8915</v>
       </c>
       <c r="G23" t="n">
-        <v>3.4676</v>
+        <v>3.7097</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9346</v>
+        <v>4.1289</v>
       </c>
       <c r="I23" t="n">
-        <v>0.533</v>
+        <v>-0.4192</v>
       </c>
       <c r="J23" t="n">
-        <v>4.6474</v>
+        <v>2.5019</v>
       </c>
       <c r="K23" t="n">
-        <v>3.216</v>
+        <v>3.1133</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4314</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1798</v>
+        <v>1.2077</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2814</v>
+        <v>1.0156</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8984</v>
+        <v>0.1922</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="R23" t="n">
         <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9036</v>
+        <v>0.3407</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8344</v>
+        <v>0.1393</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0692</v>
+        <v>0.2014</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2589</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.7266</v>
+        <v>2.2401</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0642</v>
+        <v>3.4537</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6624</v>
+        <v>-1.2136</v>
       </c>
       <c r="G24" t="n">
-        <v>3.7097</v>
+        <v>3.4676</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1289</v>
+        <v>2.9346</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4192</v>
+        <v>0.533</v>
       </c>
       <c r="J24" t="n">
-        <v>2.5019</v>
+        <v>4.6474</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1133</v>
+        <v>3.216</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6114000000000001</v>
+        <v>1.4314</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2077</v>
+        <v>-1.1798</v>
       </c>
       <c r="N24" t="n">
-        <v>1.0156</v>
+        <v>-0.2814</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1922</v>
+        <v>-0.8984</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1853</v>
+        <v>-1.8529</v>
       </c>
       <c r="R24" t="n">
         <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2801</v>
+        <v>1.1431</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2524</v>
+        <v>0.3448</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0276</v>
+        <v>0.7983</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2589</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.444</v>
+        <v>1.8805</v>
       </c>
       <c r="E25" t="n">
-        <v>2.9139</v>
+        <v>2.4243</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4699</v>
+        <v>-0.5438</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6707</v>
@@ -2404,13 +2404,13 @@
         <v>0.1853</v>
       </c>
       <c r="S25" t="n">
-        <v>1.5425</v>
+        <v>0.979</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2933</v>
+        <v>0.8036</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2492</v>
+        <v>0.1753</v>
       </c>
       <c r="V25" t="n">
         <v>1.5722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2486</v>
+        <v>0.095</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3246</v>
+        <v>-0.1287</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0759</v>
+        <v>0.2237</v>
       </c>
       <c r="G26" t="n">
         <v>1.5619</v>
@@ -2482,13 +2482,13 @@
         <v>0.3706</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2838</v>
+        <v>0.6274</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0883</v>
+        <v>0.1076</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3721</v>
+        <v>0.5198</v>
       </c>
       <c r="V26" t="n">
         <v>0.3144</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.7528</v>
+        <v>-2.2299</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0165</v>
+        <v>0.3103</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.7693</v>
+        <v>-2.5402</v>
       </c>
       <c r="G27" t="n">
         <v>1.3779</v>
@@ -2560,13 +2560,13 @@
         <v>0.1853</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5748</v>
+        <v>-0.0519</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.143</v>
+        <v>0.1508</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4318</v>
+        <v>-0.2027</v>
       </c>
       <c r="V27" t="n">
         <v>-1.8883</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>34.7988</v>
+        <v>35.45169999999999</v>
       </c>
       <c r="E28" t="n">
         <v>33.3554</v>
       </c>
       <c r="F28" t="n">
-        <v>1.443399999999999</v>
+        <v>2.096499999999999</v>
       </c>
       <c r="G28" t="n">
         <v>25.1722</v>
@@ -2608,7 +2608,7 @@
         <v>22.6757</v>
       </c>
       <c r="I28" t="n">
-        <v>2.496500000000001</v>
+        <v>2.4965</v>
       </c>
       <c r="J28" t="n">
         <v>28.9476</v>
@@ -2638,13 +2638,13 @@
         <v>7.4113</v>
       </c>
       <c r="S28" t="n">
-        <v>7.597899999999999</v>
+        <v>8.250800000000002</v>
       </c>
       <c r="T28" t="n">
         <v>3.1836</v>
       </c>
       <c r="U28" t="n">
-        <v>4.4143</v>
+        <v>5.0672</v>
       </c>
       <c r="V28" t="n">
         <v>9.440199999999997</v>
